--- a/data/trans_orig/P39B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P39B-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron el colesterol en 2012</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron el colesterol en 2012 (tasa de respuesta: 97,22%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38064</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67367</t>
+          <t>66533</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22138</t>
+          <t>22088</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47180</t>
+          <t>48151</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67852</t>
+          <t>67688</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>98651</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>139419</t>
+          <t>137656</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87193</t>
+          <t>87937</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123161</t>
+          <t>124846</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>197063</t>
+          <t>195769</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>247892</t>
+          <t>248353</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>159839</t>
+          <t>159343</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>208089</t>
+          <t>203180</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>132098</t>
+          <t>133491</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>175172</t>
+          <t>176730</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>304448</t>
+          <t>305418</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>368377</t>
+          <t>365105</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65910</t>
+          <t>67406</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101780</t>
+          <t>103332</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80770</t>
+          <t>82866</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118080</t>
+          <t>118640</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>159698</t>
+          <t>158318</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>211594</t>
+          <t>209465</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111927</t>
+          <t>110316</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>152924</t>
+          <t>149780</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>162169</t>
+          <t>161274</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>208443</t>
+          <t>206730</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>284331</t>
+          <t>284320</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>345667</t>
+          <t>347021</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55346</t>
+          <t>55344</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88386</t>
+          <t>89137</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42361</t>
+          <t>41703</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73202</t>
+          <t>71011</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>109076</t>
+          <t>105776</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152992</t>
+          <t>151784</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>157359</t>
+          <t>156989</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>206379</t>
+          <t>205663</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>135554</t>
+          <t>134872</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>184870</t>
+          <t>186169</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>306803</t>
+          <t>307700</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>377957</t>
+          <t>376615</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>222519</t>
+          <t>225754</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>278086</t>
+          <t>275863</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>255879</t>
+          <t>259280</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>313051</t>
+          <t>313591</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>494991</t>
+          <t>495218</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>571729</t>
+          <t>572330</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86904</t>
+          <t>85967</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127778</t>
+          <t>126717</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106299</t>
+          <t>105663</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150697</t>
+          <t>147629</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>203368</t>
+          <t>203224</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>263104</t>
+          <t>261573</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>170912</t>
+          <t>171228</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>223268</t>
+          <t>223009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>214373</t>
+          <t>214241</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>268458</t>
+          <t>269734</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>399310</t>
+          <t>398492</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>474221</t>
+          <t>471092</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40611</t>
+          <t>39976</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71205</t>
+          <t>70127</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32291</t>
+          <t>30737</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60421</t>
+          <t>59182</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78814</t>
+          <t>78361</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121082</t>
+          <t>119922</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>129851</t>
+          <t>133410</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175608</t>
+          <t>177991</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118674</t>
+          <t>119483</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>162981</t>
+          <t>163999</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>262747</t>
+          <t>260068</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>325759</t>
+          <t>324633</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>187408</t>
+          <t>186603</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>237835</t>
+          <t>236838</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182903</t>
+          <t>182374</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>232975</t>
+          <t>232221</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>385667</t>
+          <t>381095</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>458219</t>
+          <t>453895</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,29%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53817</t>
+          <t>55913</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89058</t>
+          <t>88835</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79819</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>119428</t>
+          <t>117651</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>142604</t>
+          <t>143775</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>197448</t>
+          <t>194806</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90242</t>
+          <t>89650</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>129709</t>
+          <t>130323</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>175378</t>
+          <t>174496</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>223498</t>
+          <t>223345</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>273323</t>
+          <t>275485</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>337753</t>
+          <t>338833</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66338</t>
+          <t>65030</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>100603</t>
+          <t>99295</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50342</t>
+          <t>50290</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81933</t>
+          <t>81061</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>125658</t>
+          <t>125155</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>174175</t>
+          <t>171827</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>172416</t>
+          <t>171195</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>219099</t>
+          <t>219761</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>167516</t>
+          <t>165569</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>214661</t>
+          <t>215498</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>349157</t>
+          <t>351918</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>421929</t>
+          <t>419189</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>193200</t>
+          <t>193501</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>243758</t>
+          <t>244556</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>247872</t>
+          <t>248996</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>301432</t>
+          <t>305282</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>454713</t>
+          <t>456835</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>531730</t>
+          <t>531479</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>63902</t>
+          <t>63507</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>97494</t>
+          <t>96886</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>93638</t>
+          <t>93542</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>135787</t>
+          <t>134826</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>166121</t>
+          <t>164940</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>221679</t>
+          <t>221132</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>142116</t>
+          <t>140949</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>187756</t>
+          <t>188937</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>234668</t>
+          <t>232994</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>291696</t>
+          <t>288415</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>390058</t>
+          <t>387445</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>465713</t>
+          <t>463797</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>228648</t>
+          <t>226252</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>293827</t>
+          <t>290279</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>169405</t>
+          <t>171232</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>228264</t>
+          <t>230013</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>418806</t>
+          <t>417052</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>502147</t>
+          <t>498978</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>597910</t>
+          <t>605963</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>692554</t>
+          <t>692145</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>551158</t>
+          <t>549350</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>640869</t>
+          <t>638239</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1179636</t>
+          <t>1175730</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1309133</t>
+          <t>1308843</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>812266</t>
+          <t>810084</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>906692</t>
+          <t>905145</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>873046</t>
+          <t>867557</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>980447</t>
+          <t>974433</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1707213</t>
+          <t>1705765</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1855063</t>
+          <t>1847576</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>305203</t>
+          <t>307669</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>377754</t>
+          <t>381128</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>397510</t>
+          <t>403908</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>475687</t>
+          <t>482977</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>722067</t>
+          <t>721642</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>828796</t>
+          <t>834057</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>556283</t>
+          <t>554730</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>646754</t>
+          <t>638688</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>837654</t>
+          <t>833056</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>941888</t>
+          <t>937074</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1422103</t>
+          <t>1418674</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1554002</t>
+          <t>1552341</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron el colesterol en 2016</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron el colesterol en 2016 (tasa de respuesta: 96,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51042</t>
+          <t>52678</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81508</t>
+          <t>82157</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34184</t>
+          <t>33322</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59566</t>
+          <t>59768</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>91612</t>
+          <t>93778</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131015</t>
+          <t>135121</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109545</t>
+          <t>105993</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>149562</t>
+          <t>147335</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>110575</t>
+          <t>110526</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>151139</t>
+          <t>150180</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>231064</t>
+          <t>228280</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>287180</t>
+          <t>287242</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>141951</t>
+          <t>141625</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>185616</t>
+          <t>184984</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>142559</t>
+          <t>146329</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>186463</t>
+          <t>188964</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>298759</t>
+          <t>299446</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>359438</t>
+          <t>359966</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61615</t>
+          <t>61387</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95426</t>
+          <t>95694</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71499</t>
+          <t>73792</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105154</t>
+          <t>107317</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>143170</t>
+          <t>142713</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>190020</t>
+          <t>191125</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82004</t>
+          <t>81272</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>117458</t>
+          <t>117955</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>119683</t>
+          <t>118871</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>162049</t>
+          <t>158592</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>210878</t>
+          <t>208312</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>263413</t>
+          <t>267524</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88760</t>
+          <t>89726</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129957</t>
+          <t>130701</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70930</t>
+          <t>70990</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108326</t>
+          <t>107783</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>170173</t>
+          <t>169262</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>224365</t>
+          <t>223091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>174289</t>
+          <t>175778</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>222744</t>
+          <t>224122</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>221435</t>
+          <t>221072</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>276702</t>
+          <t>273185</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>412141</t>
+          <t>408178</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>483011</t>
+          <t>483727</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>221621</t>
+          <t>218651</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>273421</t>
+          <t>273673</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>247170</t>
+          <t>250421</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>305064</t>
+          <t>307783</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>488579</t>
+          <t>485499</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>562287</t>
+          <t>559835</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97135</t>
+          <t>96773</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>140332</t>
+          <t>137599</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>113161</t>
+          <t>114102</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>157249</t>
+          <t>156686</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>218665</t>
+          <t>221484</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>279057</t>
+          <t>280602</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>116416</t>
+          <t>119022</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>160281</t>
+          <t>162188</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>150802</t>
+          <t>150319</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>198832</t>
+          <t>200690</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>283308</t>
+          <t>279819</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>346987</t>
+          <t>347050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40378</t>
+          <t>41181</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71571</t>
+          <t>70521</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34807</t>
+          <t>36223</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61333</t>
+          <t>62532</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83352</t>
+          <t>84997</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>122730</t>
+          <t>123563</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>170823</t>
+          <t>170174</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>216495</t>
+          <t>216655</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>163136</t>
+          <t>162939</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>211149</t>
+          <t>210743</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>348446</t>
+          <t>346706</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>413454</t>
+          <t>413885</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161598</t>
+          <t>159277</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>210271</t>
+          <t>206638</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>206895</t>
+          <t>207409</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>256936</t>
+          <t>256486</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>379746</t>
+          <t>381966</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>448349</t>
+          <t>450132</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46983</t>
+          <t>46805</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78602</t>
+          <t>78270</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60179</t>
+          <t>57556</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>94981</t>
+          <t>93732</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116548</t>
+          <t>116563</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>163752</t>
+          <t>162418</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75743</t>
+          <t>73493</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>110980</t>
+          <t>110299</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>112469</t>
+          <t>114310</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156358</t>
+          <t>156426</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>196984</t>
+          <t>198099</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>254806</t>
+          <t>254886</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,27%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64352</t>
+          <t>64589</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96479</t>
+          <t>97170</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40812</t>
+          <t>40726</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69813</t>
+          <t>69557</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>111634</t>
+          <t>109955</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>158968</t>
+          <t>156014</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>180919</t>
+          <t>179881</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>231520</t>
+          <t>229076</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>203704</t>
+          <t>202732</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>257747</t>
+          <t>256780</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>397842</t>
+          <t>399915</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>472531</t>
+          <t>469989</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>177412</t>
+          <t>180936</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>227441</t>
+          <t>227700</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>232786</t>
+          <t>228795</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>288343</t>
+          <t>285942</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>425949</t>
+          <t>422314</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>500844</t>
+          <t>495028</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88103</t>
+          <t>88348</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>127106</t>
+          <t>127068</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>123453</t>
+          <t>124602</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>169295</t>
+          <t>169876</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>222897</t>
+          <t>222063</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>283222</t>
+          <t>282549</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>114248</t>
+          <t>114788</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>155901</t>
+          <t>155005</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>137833</t>
+          <t>140146</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>187443</t>
+          <t>186981</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>264974</t>
+          <t>265428</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>328229</t>
+          <t>329797</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>277615</t>
+          <t>275330</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>346237</t>
+          <t>344121</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>207676</t>
+          <t>205152</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>263725</t>
+          <t>266370</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>501526</t>
+          <t>496716</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>590383</t>
+          <t>587464</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>681181</t>
+          <t>679112</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>771972</t>
+          <t>775191</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>744448</t>
+          <t>749818</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>846620</t>
+          <t>843817</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1448320</t>
+          <t>1452377</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1584599</t>
+          <t>1589036</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>749263</t>
+          <t>748400</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>847169</t>
+          <t>844607</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>881581</t>
+          <t>885408</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>984117</t>
+          <t>990983</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1660563</t>
+          <t>1656900</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1802332</t>
+          <t>1798411</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>323816</t>
+          <t>327146</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>398180</t>
+          <t>396105</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>401604</t>
+          <t>404629</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>481505</t>
+          <t>484273</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>749049</t>
+          <t>751428</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>856783</t>
+          <t>858651</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>424879</t>
+          <t>424779</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>503245</t>
+          <t>510386</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>563063</t>
+          <t>563411</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>653458</t>
+          <t>656108</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1014480</t>
+          <t>1012876</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1134626</t>
+          <t>1130796</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron el colesterol en 2023</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron el colesterol en 2023 (tasa de respuesta: 99,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36246</t>
+          <t>35558</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62790</t>
+          <t>63517</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48293</t>
+          <t>48808</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74034</t>
+          <t>74971</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89859</t>
+          <t>90851</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>128312</t>
+          <t>130303</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>111909</t>
+          <t>108767</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>156348</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108965</t>
+          <t>109341</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140893</t>
+          <t>140821</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>227575</t>
+          <t>228522</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>280915</t>
+          <t>284170</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>131257</t>
+          <t>130328</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>175798</t>
+          <t>175217</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>145007</t>
+          <t>144218</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>179869</t>
+          <t>179369</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>286878</t>
+          <t>285868</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>343302</t>
+          <t>342232</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86627</t>
+          <t>88694</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124678</t>
+          <t>125310</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>103995</t>
+          <t>103164</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>134142</t>
+          <t>132654</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>199829</t>
+          <t>201513</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>245507</t>
+          <t>245667</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95253</t>
+          <t>96230</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>133945</t>
+          <t>134827</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>138565</t>
+          <t>138102</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171916</t>
+          <t>171944</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>243679</t>
+          <t>243019</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>291760</t>
+          <t>291800</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55204</t>
+          <t>53914</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91350</t>
+          <t>92739</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41675</t>
+          <t>41065</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68273</t>
+          <t>65299</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102067</t>
+          <t>103875</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>146547</t>
+          <t>148490</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135104</t>
+          <t>132985</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>182526</t>
+          <t>181832</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177760</t>
+          <t>174504</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>218513</t>
+          <t>216437</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>318686</t>
+          <t>322183</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>384017</t>
+          <t>385202</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>204125</t>
+          <t>206278</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>263832</t>
+          <t>262567</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>208110</t>
+          <t>209402</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>251944</t>
+          <t>251528</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>427435</t>
+          <t>426192</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>501931</t>
+          <t>501166</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,79%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96880</t>
+          <t>99109</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>140154</t>
+          <t>138726</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120075</t>
+          <t>117932</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>154113</t>
+          <t>151682</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>226102</t>
+          <t>225922</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>277778</t>
+          <t>283338</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121814</t>
+          <t>121372</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>165639</t>
+          <t>164848</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>175513</t>
+          <t>175714</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>219106</t>
+          <t>218833</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>309425</t>
+          <t>308721</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>369056</t>
+          <t>369238</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36287</t>
+          <t>35070</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72560</t>
+          <t>69556</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19510</t>
+          <t>18734</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62949</t>
+          <t>64339</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61108</t>
+          <t>57348</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124352</t>
+          <t>120991</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167833</t>
+          <t>165707</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>218455</t>
+          <t>216305</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>84708</t>
+          <t>86196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>253081</t>
+          <t>252644</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>228443</t>
+          <t>214850</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>452105</t>
+          <t>447479</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>133614</t>
+          <t>135069</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>181669</t>
+          <t>181858</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>267782</t>
+          <t>270466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>628459</t>
+          <t>645784</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>421617</t>
+          <t>422946</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>891173</t>
+          <t>925414</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>66,41%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63080</t>
+          <t>63648</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99328</t>
+          <t>98199</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33027</t>
+          <t>35921</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>105929</t>
+          <t>104650</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96466</t>
+          <t>91751</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>189161</t>
+          <t>189833</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67859</t>
+          <t>68709</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>100331</t>
+          <t>103012</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52570</t>
+          <t>50703</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156142</t>
+          <t>156883</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122388</t>
+          <t>116581</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>239923</t>
+          <t>239909</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31655</t>
+          <t>31864</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61457</t>
+          <t>59070</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40416</t>
+          <t>40320</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65820</t>
+          <t>66474</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>79629</t>
+          <t>78901</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115455</t>
+          <t>114876</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>173556</t>
+          <t>170162</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>225356</t>
+          <t>225905</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>174358</t>
+          <t>171890</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>216472</t>
+          <t>216639</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>357021</t>
+          <t>357944</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>428987</t>
+          <t>428521</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>204611</t>
+          <t>204341</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>258090</t>
+          <t>255780</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>267203</t>
+          <t>266312</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>315446</t>
+          <t>316418</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>488493</t>
+          <t>486489</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>559488</t>
+          <t>554086</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>33,9%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>116010</t>
+          <t>117208</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>162255</t>
+          <t>159449</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>135218</t>
+          <t>135921</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>172232</t>
+          <t>172721</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>262758</t>
+          <t>260895</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>316532</t>
+          <t>317374</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>116934</t>
+          <t>115815</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>158566</t>
+          <t>155084</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>179844</t>
+          <t>178565</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>225957</t>
+          <t>225331</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>308459</t>
+          <t>304694</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>366624</t>
+          <t>365205</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>183681</t>
+          <t>182778</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>243279</t>
+          <t>245524</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>167134</t>
+          <t>166057</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>239084</t>
+          <t>240467</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>369199</t>
+          <t>367569</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>464796</t>
+          <t>466982</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>632650</t>
+          <t>627648</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>735755</t>
+          <t>728154</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>537522</t>
+          <t>549880</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>758835</t>
+          <t>761236</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1201249</t>
+          <t>1216635</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1454118</t>
+          <t>1451236</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>718006</t>
+          <t>724041</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>823305</t>
+          <t>820390</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>945251</t>
+          <t>938509</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1648912</t>
+          <t>1526969</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1707532</t>
+          <t>1707786</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2462643</t>
+          <t>2373005</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>41,45%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>397913</t>
+          <t>401723</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>480332</t>
+          <t>477742</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>365925</t>
+          <t>381960</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>528749</t>
+          <t>528450</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>793730</t>
+          <t>804281</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>973683</t>
+          <t>975590</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>433539</t>
+          <t>433501</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>515529</t>
+          <t>510450</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>507001</t>
+          <t>536065</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>727028</t>
+          <t>728462</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>999985</t>
+          <t>993480</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1206807</t>
+          <t>1206860</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">

--- a/data/trans_orig/P39B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P39B-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38594</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66533</t>
+          <t>67092</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22088</t>
+          <t>22382</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48151</t>
+          <t>46965</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67688</t>
+          <t>66559</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105972</t>
+          <t>104954</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98651</t>
+          <t>97367</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>137656</t>
+          <t>135234</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87937</t>
+          <t>87775</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>124846</t>
+          <t>124078</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>195769</t>
+          <t>194477</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>248353</t>
+          <t>249141</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>159343</t>
+          <t>158271</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>203180</t>
+          <t>203770</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>133491</t>
+          <t>132649</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>176730</t>
+          <t>175438</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>305418</t>
+          <t>302068</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>365105</t>
+          <t>367634</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,25%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67406</t>
+          <t>67739</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>103332</t>
+          <t>102911</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82866</t>
+          <t>81488</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118640</t>
+          <t>118338</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>158318</t>
+          <t>158627</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>209465</t>
+          <t>210755</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>110316</t>
+          <t>111048</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>149780</t>
+          <t>151241</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>161274</t>
+          <t>161828</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>206730</t>
+          <t>206221</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>284320</t>
+          <t>283478</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>347021</t>
+          <t>345056</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,27%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55344</t>
+          <t>55962</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89137</t>
+          <t>89798</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41703</t>
+          <t>42022</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71011</t>
+          <t>70653</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105776</t>
+          <t>104907</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151784</t>
+          <t>148854</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>156989</t>
+          <t>158214</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>205663</t>
+          <t>205817</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>134872</t>
+          <t>136477</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>186169</t>
+          <t>183121</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>307700</t>
+          <t>307899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>376615</t>
+          <t>374898</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>225754</t>
+          <t>222893</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>275863</t>
+          <t>277452</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>259280</t>
+          <t>255657</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>313591</t>
+          <t>313672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>495218</t>
+          <t>497287</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>572330</t>
+          <t>571101</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,25%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85967</t>
+          <t>85853</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126717</t>
+          <t>128716</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105663</t>
+          <t>106606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147629</t>
+          <t>148230</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>203224</t>
+          <t>202402</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>261573</t>
+          <t>259952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>171228</t>
+          <t>171657</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>223009</t>
+          <t>221156</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>214241</t>
+          <t>212332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>269734</t>
+          <t>269559</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>398492</t>
+          <t>401111</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>471092</t>
+          <t>472818</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39976</t>
+          <t>40814</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70127</t>
+          <t>71389</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30737</t>
+          <t>31221</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59182</t>
+          <t>59203</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78361</t>
+          <t>79404</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>119922</t>
+          <t>119844</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>133410</t>
+          <t>134495</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177991</t>
+          <t>179350</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119483</t>
+          <t>119286</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>163999</t>
+          <t>163774</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>260068</t>
+          <t>263936</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>324633</t>
+          <t>326541</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>186603</t>
+          <t>184769</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>236838</t>
+          <t>236158</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182374</t>
+          <t>185919</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>232221</t>
+          <t>236093</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>381095</t>
+          <t>381864</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>453895</t>
+          <t>452735</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55913</t>
+          <t>56155</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88835</t>
+          <t>90608</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>77966</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>117651</t>
+          <t>117827</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>143775</t>
+          <t>146038</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>194806</t>
+          <t>194704</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>89650</t>
+          <t>88557</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>130323</t>
+          <t>129352</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>174496</t>
+          <t>172872</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>223345</t>
+          <t>221420</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>275485</t>
+          <t>277976</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>338833</t>
+          <t>341905</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65030</t>
+          <t>65035</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99295</t>
+          <t>100572</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50290</t>
+          <t>50237</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81061</t>
+          <t>82636</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>125155</t>
+          <t>126032</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>171827</t>
+          <t>168918</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>171195</t>
+          <t>171884</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>219761</t>
+          <t>218878</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>165569</t>
+          <t>165150</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>215498</t>
+          <t>215308</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>351918</t>
+          <t>351644</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>419189</t>
+          <t>422534</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>193501</t>
+          <t>192394</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>244556</t>
+          <t>245458</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>248996</t>
+          <t>248717</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>305282</t>
+          <t>300772</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>456835</t>
+          <t>458571</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>531479</t>
+          <t>533162</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>63507</t>
+          <t>63207</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96886</t>
+          <t>96723</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>93542</t>
+          <t>93950</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>134826</t>
+          <t>133662</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>164940</t>
+          <t>167155</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>221132</t>
+          <t>220248</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>140949</t>
+          <t>141111</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>188937</t>
+          <t>187335</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>232994</t>
+          <t>233946</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>288415</t>
+          <t>291399</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>387445</t>
+          <t>385686</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>463797</t>
+          <t>459279</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>226252</t>
+          <t>229444</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>290279</t>
+          <t>290958</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>171232</t>
+          <t>171265</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>230013</t>
+          <t>227010</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>417052</t>
+          <t>418563</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>498978</t>
+          <t>498881</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>605963</t>
+          <t>604198</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>692145</t>
+          <t>697755</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>549350</t>
+          <t>550017</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>638239</t>
+          <t>640977</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1175730</t>
+          <t>1179294</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1308843</t>
+          <t>1303386</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>810084</t>
+          <t>810230</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>905145</t>
+          <t>911948</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>867557</t>
+          <t>867415</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>974433</t>
+          <t>970161</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1705765</t>
+          <t>1706478</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1847576</t>
+          <t>1850039</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,25%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>307669</t>
+          <t>305360</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>381128</t>
+          <t>376172</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>403908</t>
+          <t>398739</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>482977</t>
+          <t>478749</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>721642</t>
+          <t>723066</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>834057</t>
+          <t>829926</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>554730</t>
+          <t>548839</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>638688</t>
+          <t>638559</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>833056</t>
+          <t>830518</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>937074</t>
+          <t>936919</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1418674</t>
+          <t>1418108</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1552341</t>
+          <t>1550762</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52678</t>
+          <t>52217</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82157</t>
+          <t>83697</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33322</t>
+          <t>32331</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59768</t>
+          <t>57805</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93778</t>
+          <t>92644</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135121</t>
+          <t>135516</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105993</t>
+          <t>108477</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>147335</t>
+          <t>148143</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>110526</t>
+          <t>110917</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>150180</t>
+          <t>151354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>228280</t>
+          <t>230854</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>287242</t>
+          <t>289119</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>141625</t>
+          <t>142290</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>184984</t>
+          <t>188046</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>146329</t>
+          <t>144817</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>188964</t>
+          <t>188153</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>299446</t>
+          <t>298027</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>359966</t>
+          <t>359028</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,59%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61387</t>
+          <t>62995</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95694</t>
+          <t>93855</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73792</t>
+          <t>72734</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107317</t>
+          <t>107920</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>142713</t>
+          <t>140910</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>191125</t>
+          <t>190261</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81272</t>
+          <t>82762</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>117955</t>
+          <t>116911</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>118871</t>
+          <t>119268</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>158592</t>
+          <t>158941</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>208312</t>
+          <t>210144</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>267524</t>
+          <t>265914</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89726</t>
+          <t>88896</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130701</t>
+          <t>127675</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70990</t>
+          <t>69964</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107783</t>
+          <t>106855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169262</t>
+          <t>171283</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>223091</t>
+          <t>224504</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>175778</t>
+          <t>175924</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>224122</t>
+          <t>225239</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>221072</t>
+          <t>222942</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>273185</t>
+          <t>274787</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>408178</t>
+          <t>406899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>483727</t>
+          <t>484489</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>218651</t>
+          <t>219286</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>273673</t>
+          <t>272843</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>250421</t>
+          <t>248230</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>307783</t>
+          <t>307462</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>485499</t>
+          <t>490382</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>559835</t>
+          <t>565879</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96773</t>
+          <t>96233</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>137599</t>
+          <t>135689</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>114102</t>
+          <t>114970</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>156686</t>
+          <t>158622</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>221484</t>
+          <t>219937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>280602</t>
+          <t>278912</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>119022</t>
+          <t>119709</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162188</t>
+          <t>162443</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>150319</t>
+          <t>151649</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>200690</t>
+          <t>200808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>279819</t>
+          <t>285459</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>347050</t>
+          <t>350671</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,27%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41181</t>
+          <t>40739</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70521</t>
+          <t>69780</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36223</t>
+          <t>35325</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62532</t>
+          <t>62000</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>84997</t>
+          <t>82602</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123563</t>
+          <t>121921</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>170174</t>
+          <t>169276</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>216655</t>
+          <t>218747</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>162939</t>
+          <t>165208</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>210743</t>
+          <t>211632</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>346706</t>
+          <t>349015</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>413885</t>
+          <t>415116</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>159277</t>
+          <t>159732</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>206638</t>
+          <t>207593</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207409</t>
+          <t>209472</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>256486</t>
+          <t>258382</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>381966</t>
+          <t>379851</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>450132</t>
+          <t>448705</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,68%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46805</t>
+          <t>46713</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78270</t>
+          <t>78051</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57556</t>
+          <t>59630</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>93732</t>
+          <t>92769</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116563</t>
+          <t>114594</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>162418</t>
+          <t>159216</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>73493</t>
+          <t>74175</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>110299</t>
+          <t>111070</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>114310</t>
+          <t>113460</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156426</t>
+          <t>155536</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>198099</t>
+          <t>199919</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>254886</t>
+          <t>254439</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64589</t>
+          <t>64176</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97170</t>
+          <t>97175</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40726</t>
+          <t>40065</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69557</t>
+          <t>70674</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>109955</t>
+          <t>111624</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>156014</t>
+          <t>156328</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>179881</t>
+          <t>181808</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>229076</t>
+          <t>228450</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>202732</t>
+          <t>203597</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>256780</t>
+          <t>256124</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>399915</t>
+          <t>400313</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>469989</t>
+          <t>471970</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>180936</t>
+          <t>180428</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>227700</t>
+          <t>226803</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>228795</t>
+          <t>231290</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>285942</t>
+          <t>285681</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>422314</t>
+          <t>423080</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>495028</t>
+          <t>496030</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88348</t>
+          <t>87455</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>127068</t>
+          <t>128626</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>124602</t>
+          <t>122675</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>169876</t>
+          <t>168954</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>222063</t>
+          <t>221529</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>282549</t>
+          <t>280959</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>114788</t>
+          <t>115230</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>155005</t>
+          <t>158282</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>140146</t>
+          <t>139961</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>186981</t>
+          <t>187765</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>265428</t>
+          <t>265596</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>329797</t>
+          <t>329111</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>275330</t>
+          <t>279284</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>344121</t>
+          <t>346593</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>205152</t>
+          <t>204120</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>266370</t>
+          <t>266079</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>496716</t>
+          <t>497416</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>587464</t>
+          <t>586845</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>679112</t>
+          <t>671747</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>775191</t>
+          <t>767654</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>749818</t>
+          <t>740877</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>843817</t>
+          <t>841794</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1452377</t>
+          <t>1445039</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1589036</t>
+          <t>1581714</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>748400</t>
+          <t>746404</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>844607</t>
+          <t>842209</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>885408</t>
+          <t>883222</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>990983</t>
+          <t>985047</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1656900</t>
+          <t>1654322</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1798411</t>
+          <t>1801821</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>327146</t>
+          <t>329157</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>396105</t>
+          <t>400342</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>404629</t>
+          <t>402037</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>484273</t>
+          <t>484847</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>751428</t>
+          <t>746312</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>858651</t>
+          <t>854218</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>424779</t>
+          <t>422618</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>510386</t>
+          <t>503722</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>563411</t>
+          <t>567182</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>656108</t>
+          <t>662612</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1012876</t>
+          <t>1017995</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1130796</t>
+          <t>1136017</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -8011,32 +8011,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>47846</t>
+          <t>55119</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35558</t>
+          <t>41632</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63517</t>
+          <t>70749</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8046,32 +8046,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>60556</t>
+          <t>64429</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48808</t>
+          <t>51527</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74971</t>
+          <t>80761</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8081,32 +8081,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>108402</t>
+          <t>119548</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90851</t>
+          <t>100714</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>130303</t>
+          <t>143207</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -8124,32 +8124,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>131899</t>
+          <t>137762</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108767</t>
+          <t>117621</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>156348</t>
+          <t>160878</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8159,32 +8159,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>123343</t>
+          <t>131075</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>109341</t>
+          <t>116436</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140821</t>
+          <t>149178</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8194,32 +8194,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>255242</t>
+          <t>268837</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>228522</t>
+          <t>243745</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>284170</t>
+          <t>296038</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -8237,32 +8237,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>151450</t>
+          <t>162118</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>130328</t>
+          <t>141348</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>175217</t>
+          <t>184866</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8272,32 +8272,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>161955</t>
+          <t>178370</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>144218</t>
+          <t>159973</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>179369</t>
+          <t>196626</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8307,32 +8307,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>313405</t>
+          <t>340489</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>285868</t>
+          <t>313655</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>342232</t>
+          <t>369495</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,39%</t>
         </is>
       </c>
     </row>
@@ -8350,32 +8350,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>105129</t>
+          <t>116007</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88694</t>
+          <t>99294</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>125310</t>
+          <t>137241</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8385,32 +8385,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>117647</t>
+          <t>125936</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>103164</t>
+          <t>111329</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>132654</t>
+          <t>143531</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8420,32 +8420,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>222776</t>
+          <t>241943</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>201513</t>
+          <t>218456</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>245667</t>
+          <t>270210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -8463,32 +8463,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>113486</t>
+          <t>122325</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96230</t>
+          <t>103952</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>134827</t>
+          <t>142586</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8498,32 +8498,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>154780</t>
+          <t>164121</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>138102</t>
+          <t>147036</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171944</t>
+          <t>182335</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8533,32 +8533,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>268266</t>
+          <t>286445</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>243019</t>
+          <t>260678</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>291800</t>
+          <t>312223</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -8576,17 +8576,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>549810</t>
+          <t>593331</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>549810</t>
+          <t>593331</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>549810</t>
+          <t>593331</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8611,17 +8611,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>618281</t>
+          <t>663930</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>618281</t>
+          <t>663930</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>618281</t>
+          <t>663930</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8646,17 +8646,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1168090</t>
+          <t>1257262</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1168090</t>
+          <t>1257262</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1168090</t>
+          <t>1257262</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8693,32 +8693,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>71032</t>
+          <t>77211</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53914</t>
+          <t>60472</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92739</t>
+          <t>97423</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8728,32 +8728,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>52695</t>
+          <t>58255</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41065</t>
+          <t>44899</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65299</t>
+          <t>72218</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8763,32 +8763,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>123727</t>
+          <t>135467</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103875</t>
+          <t>113945</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>148490</t>
+          <t>160893</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -8806,32 +8806,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>156815</t>
+          <t>179967</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>132985</t>
+          <t>156629</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>181832</t>
+          <t>206062</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8841,32 +8841,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>195767</t>
+          <t>218447</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>174504</t>
+          <t>195333</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>216437</t>
+          <t>241441</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8876,32 +8876,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>352582</t>
+          <t>398415</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>322183</t>
+          <t>366423</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>385202</t>
+          <t>436289</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -8919,32 +8919,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>233068</t>
+          <t>249170</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>206278</t>
+          <t>223893</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>262567</t>
+          <t>278669</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8954,32 +8954,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>229537</t>
+          <t>257804</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>209402</t>
+          <t>236286</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>251528</t>
+          <t>282031</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8989,32 +8989,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>462606</t>
+          <t>506974</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>426192</t>
+          <t>471797</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>501166</t>
+          <t>544183</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -9032,32 +9032,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>116719</t>
+          <t>127106</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>99109</t>
+          <t>107010</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>138726</t>
+          <t>148879</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9067,32 +9067,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>135580</t>
+          <t>150159</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117932</t>
+          <t>131725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>151682</t>
+          <t>170424</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9102,32 +9102,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>252299</t>
+          <t>277264</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>225922</t>
+          <t>248396</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>283338</t>
+          <t>304223</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -9145,32 +9145,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>141014</t>
+          <t>155035</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121372</t>
+          <t>132287</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>164848</t>
+          <t>178429</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9180,32 +9180,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>196218</t>
+          <t>215733</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>175714</t>
+          <t>195973</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>218833</t>
+          <t>238407</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9215,32 +9215,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>337232</t>
+          <t>370768</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>308721</t>
+          <t>341647</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>369238</t>
+          <t>407044</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -9258,17 +9258,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>718648</t>
+          <t>788489</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>718648</t>
+          <t>788489</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>718648</t>
+          <t>788489</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9293,17 +9293,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>809797</t>
+          <t>900398</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>809797</t>
+          <t>900398</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>809797</t>
+          <t>900398</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9328,17 +9328,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1528445</t>
+          <t>1688887</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1528445</t>
+          <t>1688887</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1528445</t>
+          <t>1688887</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9375,32 +9375,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>50327</t>
+          <t>59234</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35070</t>
+          <t>41729</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69556</t>
+          <t>79787</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9410,32 +9410,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>44147</t>
+          <t>49225</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18734</t>
+          <t>38351</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64339</t>
+          <t>62255</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9445,32 +9445,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>94474</t>
+          <t>108459</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57348</t>
+          <t>89319</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120991</t>
+          <t>134475</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -9488,32 +9488,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>190977</t>
+          <t>212106</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>165707</t>
+          <t>185356</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>216305</t>
+          <t>238541</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9523,32 +9523,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>181682</t>
+          <t>209820</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86196</t>
+          <t>186837</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>252644</t>
+          <t>232141</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9558,32 +9558,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>372659</t>
+          <t>421925</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>214850</t>
+          <t>388752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>447479</t>
+          <t>461365</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>34,83%</t>
         </is>
       </c>
     </row>
@@ -9601,32 +9601,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>157251</t>
+          <t>173094</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>135069</t>
+          <t>150279</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>181858</t>
+          <t>198884</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9636,32 +9636,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>420960</t>
+          <t>208322</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>270466</t>
+          <t>186128</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>645784</t>
+          <t>230845</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9671,32 +9671,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>578212</t>
+          <t>381416</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>422946</t>
+          <t>346909</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>925414</t>
+          <t>413487</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -9714,32 +9714,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>78594</t>
+          <t>88695</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63648</t>
+          <t>72647</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>98199</t>
+          <t>108850</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9749,32 +9749,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>74541</t>
+          <t>93886</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35921</t>
+          <t>79418</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104650</t>
+          <t>110063</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9784,32 +9784,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>153134</t>
+          <t>182581</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>91751</t>
+          <t>159859</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>189833</t>
+          <t>208719</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -9827,32 +9827,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>83050</t>
+          <t>95656</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>68709</t>
+          <t>78577</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>103012</t>
+          <t>116452</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9862,32 +9862,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>111960</t>
+          <t>134438</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50703</t>
+          <t>117219</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156883</t>
+          <t>153562</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9897,32 +9897,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>195010</t>
+          <t>230094</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>116581</t>
+          <t>203057</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>239909</t>
+          <t>257775</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -9940,17 +9940,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>560198</t>
+          <t>628785</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>560198</t>
+          <t>628785</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>560198</t>
+          <t>628785</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9975,17 +9975,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>833291</t>
+          <t>695691</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>833291</t>
+          <t>695691</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>833291</t>
+          <t>695691</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10010,17 +10010,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1393489</t>
+          <t>1324476</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1393489</t>
+          <t>1324476</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1393489</t>
+          <t>1324476</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>43819</t>
+          <t>50669</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31864</t>
+          <t>37824</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59070</t>
+          <t>68865</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>52005</t>
+          <t>54734</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40320</t>
+          <t>41819</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66474</t>
+          <t>67535</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>95824</t>
+          <t>105403</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78901</t>
+          <t>86204</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114876</t>
+          <t>125680</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -10170,32 +10170,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>197137</t>
+          <t>209200</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>170162</t>
+          <t>183399</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>225905</t>
+          <t>236337</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10205,32 +10205,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>193486</t>
+          <t>210346</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>171890</t>
+          <t>187908</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>216639</t>
+          <t>232081</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10240,32 +10240,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>390623</t>
+          <t>419545</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>357944</t>
+          <t>386063</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>428521</t>
+          <t>455345</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -10283,32 +10283,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>230572</t>
+          <t>240708</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>204341</t>
+          <t>216891</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>255780</t>
+          <t>269175</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10318,32 +10318,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>292254</t>
+          <t>312411</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>266312</t>
+          <t>290653</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>316418</t>
+          <t>337873</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10353,32 +10353,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>522826</t>
+          <t>553119</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>486489</t>
+          <t>515554</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>554086</t>
+          <t>591929</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -10396,32 +10396,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>136972</t>
+          <t>143375</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>117208</t>
+          <t>122594</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>159449</t>
+          <t>168094</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10431,32 +10431,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>153071</t>
+          <t>164498</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>135921</t>
+          <t>146530</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>172721</t>
+          <t>186723</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10466,32 +10466,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>290043</t>
+          <t>307873</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>260895</t>
+          <t>281456</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>317374</t>
+          <t>339606</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -10509,32 +10509,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>134431</t>
+          <t>135989</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>115815</t>
+          <t>116894</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>155084</t>
+          <t>158373</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10544,32 +10544,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>200640</t>
+          <t>215204</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>178565</t>
+          <t>194271</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>225331</t>
+          <t>237625</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10579,32 +10579,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>335071</t>
+          <t>351193</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>304694</t>
+          <t>320495</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>365205</t>
+          <t>383517</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -10622,17 +10622,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>742932</t>
+          <t>779941</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>742932</t>
+          <t>779941</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>742932</t>
+          <t>779941</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10657,17 +10657,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>891456</t>
+          <t>957193</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>891456</t>
+          <t>957193</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>891456</t>
+          <t>957193</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10692,17 +10692,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1634388</t>
+          <t>1737134</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1634388</t>
+          <t>1737134</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1634388</t>
+          <t>1737134</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10739,102 +10739,102 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>213024</t>
+          <t>242233</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>182778</t>
+          <t>212366</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>245524</t>
+          <t>279917</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>7,61%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>10,03%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>226643</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>199850</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>253360</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>6,21%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>7,88%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>468877</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>427086</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>512751</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>7,11%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>9,55%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>209403</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>166057</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>240467</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>422427</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>367569</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>466982</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -10852,32 +10852,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>676828</t>
+          <t>739034</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>627648</t>
+          <t>686861</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>728154</t>
+          <t>788962</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10887,32 +10887,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>694278</t>
+          <t>769688</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>549880</t>
+          <t>728765</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>761236</t>
+          <t>808484</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10922,32 +10922,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1371106</t>
+          <t>1508722</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1216635</t>
+          <t>1444845</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1451236</t>
+          <t>1574391</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -10965,32 +10965,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>772343</t>
+          <t>825091</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>724041</t>
+          <t>775491</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>820390</t>
+          <t>876826</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11000,32 +11000,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1104707</t>
+          <t>956906</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>938509</t>
+          <t>917858</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1526969</t>
+          <t>1009218</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11035,32 +11035,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1877049</t>
+          <t>1781997</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1707786</t>
+          <t>1722448</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2373005</t>
+          <t>1858914</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>30,94%</t>
         </is>
       </c>
     </row>
@@ -11078,32 +11078,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>437413</t>
+          <t>475183</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>401723</t>
+          <t>436800</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>477742</t>
+          <t>520572</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11113,32 +11113,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>480839</t>
+          <t>534479</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>381960</t>
+          <t>499592</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>528450</t>
+          <t>568656</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11148,32 +11148,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>918252</t>
+          <t>1009662</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>804281</t>
+          <t>958869</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>975590</t>
+          <t>1065345</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -11191,32 +11191,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>471981</t>
+          <t>509005</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>433501</t>
+          <t>473062</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>510450</t>
+          <t>552231</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11226,32 +11226,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>663598</t>
+          <t>729495</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>536065</t>
+          <t>686725</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>728462</t>
+          <t>769264</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11261,32 +11261,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1135578</t>
+          <t>1238500</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>993480</t>
+          <t>1173741</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1206860</t>
+          <t>1296075</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -11304,17 +11304,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2571589</t>
+          <t>2790546</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2571589</t>
+          <t>2790546</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2571589</t>
+          <t>2790546</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11339,17 +11339,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3152825</t>
+          <t>3217212</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3152825</t>
+          <t>3217212</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3152825</t>
+          <t>3217212</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11374,17 +11374,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>5724413</t>
+          <t>6007758</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5724413</t>
+          <t>6007758</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5724413</t>
+          <t>6007758</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
